--- a/backend/watched_files/electronics_mrp_data.xlsx
+++ b/backend/watched_files/electronics_mrp_data.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item_Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Forecast" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_POs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Item_Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Demand_Forecast" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open_POs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sales_History" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,13 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,14 +478,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Laptop Pro 15</t>
+          <t>Smart Speaker Pro</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
         <v>50</v>
@@ -487,7 +496,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>850</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -498,14 +507,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tablet X10</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -516,7 +525,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>420</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -527,14 +536,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Motherboard A</t>
+          <t>Audio Board</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -545,7 +554,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +565,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Display Assembly 15in</t>
+          <t>Battery Pack</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -574,7 +583,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +594,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tablet Motherboard</t>
+          <t>Driver Module</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -603,7 +612,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -614,14 +623,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Display Assembly 10in</t>
+          <t>Charging Case</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -632,7 +641,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
         <v>200</v>
@@ -661,7 +670,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +681,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RAM Module 16GB</t>
+          <t>Memory Module</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -690,7 +699,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +710,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSD 512GB</t>
+          <t>Lithium Cell</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -719,7 +728,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +739,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Battery Cell</t>
+          <t>Speaker Cone</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -740,7 +749,7 @@
         <v>150</v>
       </c>
       <c r="E11" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -748,7 +757,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +768,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aluminum Casing</t>
+          <t>PCB Blank</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -788,14 +797,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Retail Box Large</t>
+          <t>Retail Box</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E13" t="n">
         <v>1000</v>
@@ -806,7 +815,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +826,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Retail Box Medium</t>
+          <t>Foam Insert</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E14" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -835,7 +844,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +931,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RAW005</t>
+          <t>PKG001</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -932,12 +941,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELC001</t>
+          <t>ELC002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PKG001</t>
+          <t>SUB003</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -952,7 +961,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUB003</t>
+          <t>SUB004</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -967,7 +976,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SUB004</t>
+          <t>PKG002</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -977,12 +986,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELC002</t>
+          <t>SUB001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RAW004</t>
+          <t>RAW001</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -992,16 +1001,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELC002</t>
+          <t>SUB001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PKG002</t>
+          <t>RAW002</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1021,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RAW001</t>
+          <t>RAW005</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1022,27 +1031,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SUB001</t>
+          <t>SUB002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RAW002</t>
+          <t>RAW003</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUB001</t>
+          <t>SUB003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RAW003</t>
+          <t>RAW001</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1057,7 +1066,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RAW001</t>
+          <t>RAW005</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1067,27 +1076,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SUB003</t>
+          <t>SUB004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RAW002</t>
+          <t>RAW003</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUB003</t>
+          <t>SUB004</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RAW003</t>
+          <t>RAW005</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1137,13 +1146,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -1153,13 +1162,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1169,13 +1178,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -1185,13 +1194,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -1201,13 +1210,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -1217,13 +1226,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -1233,13 +1242,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -1249,13 +1258,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
@@ -1265,13 +1274,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>150</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11">
@@ -1281,13 +1290,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12">
@@ -1297,13 +1306,13 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>800</v>
+      </c>
+      <c r="C12" t="n">
         <v>80</v>
       </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13">
@@ -1313,13 +1322,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D13" t="n">
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="14">
@@ -1329,13 +1338,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="C14" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D14" t="n">
-        <v>600</v>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
@@ -1406,28 +1415,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
         <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1437,28 +1446,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="n">
         <v>35</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>40</v>
-      </c>
-      <c r="G3" t="n">
-        <v>32</v>
-      </c>
-      <c r="H3" t="n">
-        <v>38</v>
-      </c>
-      <c r="I3" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1472,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,7 +1529,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chip Supplier Co</t>
+          <t>ChipCo</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1528,7 +1537,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1545,12 +1554,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RAW002</t>
+          <t>RAW003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Memory Corp</t>
+          <t>PowerCell</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1558,7 +1567,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1575,20 +1584,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RAW003</t>
+          <t>PKG001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Storage Ltd</t>
+          <t>PackPro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1605,116 +1614,237 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RAW004</t>
+          <t>SUB001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Battery Tech</t>
+          <t>BoardWorks</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PO-2005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SUB001</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Board Makers Inc</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PO-2006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RAW005</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Metal Works</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PO-2007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PKG001</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Packaging Co</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>W-16</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>W-15</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>W-14</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>W-13</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>W-12</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>W-11</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>W-10</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>W-9</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>W-8</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>W-7</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>W-6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>W-5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>W-4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ELC001</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ELC002</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K3" t="n">
+        <v>28</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>30</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
